--- a/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 23,89</t>
+          <t>-7,06; 25,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 8,94</t>
+          <t>-11,24; 8,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 14,64</t>
+          <t>-2,27; 15,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 27,09</t>
+          <t>-11,71; 26,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,95; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,14 +695,14 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 480,64</t>
+          <t>-73,9; 583,37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,98; -2,34</t>
+          <t>-13,45; -2,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 6,13</t>
+          <t>-5,51; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -1,1</t>
+          <t>-15,35; -1,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 5,75</t>
+          <t>-12,86; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,19 +790,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,77</t>
+          <t>-100,0; 34,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 150,97</t>
+          <t>-82,82; 107,01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 15,77</t>
+          <t>-1,8; 14,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 2,73</t>
+          <t>-10,9; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 19,7</t>
+          <t>-0,06; 20,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 8,22</t>
+          <t>-8,91; 9,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,36</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -0,21</t>
+          <t>-18,45; -0,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 17,05</t>
+          <t>-3,06; 17,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 14,66</t>
+          <t>-10,71; 14,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 907,7</t>
+          <t>-43,14; 817,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 416,29</t>
+          <t>-75,3; 440,27</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 28,81</t>
+          <t>-5,64; 28,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 14,19</t>
+          <t>-7,18; 14,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 23,5</t>
+          <t>-28,43; 24,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 13,3</t>
+          <t>-17,66; 15,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 710,18</t>
+          <t>-39,23; 693,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,19 +1090,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 38,03</t>
+          <t>-33,18; 39,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 20,72</t>
+          <t>-22,5; 22,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 12,12</t>
+          <t>-6,34; 11,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 7,1</t>
+          <t>-13,76; 8,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 24,17</t>
+          <t>-10,97; 22,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 435,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 201,71</t>
+          <t>-43,86; 172,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 8,31</t>
+          <t>-6,79; 7,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 7,09</t>
+          <t>-4,24; 6,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,28; -0,48</t>
+          <t>-22,09; 0,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 5,19</t>
+          <t>-18,28; 4,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,02; 275,94</t>
+          <t>-63,75; 287,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,87; 656,27</t>
+          <t>-77,99; 579,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-70,41; -0,12</t>
+          <t>-68,87; 4,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 35,59</t>
+          <t>-63,26; 35,81</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 3,68</t>
+          <t>-10,76; 3,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,88</t>
+          <t>-5,78; 10,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 12,29</t>
+          <t>-12,29; 12,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 8,07</t>
+          <t>-12,03; 8,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 56,2</t>
+          <t>-67,9; 65,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 190,09</t>
+          <t>-46,04; 205,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 50,06</t>
+          <t>-31,66; 50,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,48</t>
+          <t>-13,68; 11,04</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,07</t>
+          <t>-2,55; 3,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,05</t>
+          <t>-3,59; 2,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,28</t>
+          <t>-5,43; 4,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,65</t>
+          <t>-7,81; 3,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 77,58</t>
+          <t>-30,53; 69,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 44,06</t>
+          <t>-46,43; 50,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 24,11</t>
+          <t>-25,77; 23,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 13,52</t>
+          <t>-22,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 25,1</t>
+          <t>-6,85; 23,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 8,78</t>
+          <t>-12,37; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 15,14</t>
+          <t>-2,1; 14,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 26,23</t>
+          <t>-10,38; 26,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-68,51; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 583,37</t>
+          <t>-68,8; 652,31</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -2,44</t>
+          <t>-13,16; -2,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 5,98</t>
+          <t>-6,17; 6,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -1,28</t>
+          <t>-16,11; -1,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 4,46</t>
+          <t>-12,0; 5,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,98</t>
+          <t>-100,0; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,82; 107,01</t>
+          <t>-85,39; 148,06</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 14,78</t>
+          <t>-1,33; 14,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 2,36</t>
+          <t>-11,17; 3,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 20,21</t>
+          <t>-0,71; 19,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 9,87</t>
+          <t>-9,28; 8,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -0,03</t>
+          <t>-18,48; 0,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 17,99</t>
+          <t>-3,13; 17,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 14,98</t>
+          <t>-11,63; 14,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 116,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 817,44</t>
+          <t>-46,58; 792,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 440,27</t>
+          <t>-78,35; 519,24</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 28,35</t>
+          <t>-10,69; 25,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 14,24</t>
+          <t>-7,09; 14,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 24,43</t>
+          <t>-27,69; 21,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 15,28</t>
+          <t>-19,08; 14,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 693,49</t>
+          <t>-46,71; 621,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 39,43</t>
+          <t>-35,03; 35,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 22,52</t>
+          <t>-23,24; 22,34</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 11,52</t>
+          <t>-6,39; 12,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 8,61</t>
+          <t>-13,42; 6,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 22,54</t>
+          <t>-9,03; 21,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,99</t>
+          <t>0,0; 12,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 360,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 172,97</t>
+          <t>-34,22; 195,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,73</t>
+          <t>-6,95; 7,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,88</t>
+          <t>-4,62; 8,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 0,11</t>
+          <t>-22,06; 0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 4,8</t>
+          <t>-17,24; 5,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 287,55</t>
+          <t>-68,29; 235,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-77,99; 579,23</t>
+          <t>-80,77; 816,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 4,55</t>
+          <t>-71,22; 4,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 35,81</t>
+          <t>-61,08; 36,54</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,91</t>
+          <t>-11,02; 3,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 10,09</t>
+          <t>-5,39; 10,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 12,35</t>
+          <t>-12,37; 13,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 8,64</t>
+          <t>-12,44; 8,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 65,02</t>
+          <t>-71,02; 55,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 205,58</t>
+          <t>-44,83; 237,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 50,82</t>
+          <t>-32,08; 51,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 11,04</t>
+          <t>-14,2; 11,25</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,63</t>
+          <t>-2,48; 3,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,42</t>
+          <t>-3,58; 2,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,1</t>
+          <t>-5,4; 4,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,82</t>
+          <t>-7,65; 4,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 69,16</t>
+          <t>-31,15; 75,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 50,32</t>
+          <t>-45,53; 46,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 23,68</t>
+          <t>-24,55; 26,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 13,13</t>
+          <t>-22,3; 15,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 23,65</t>
+          <t>-6,71; 23,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 8,24</t>
+          <t>-11,73; 8,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 14,43</t>
+          <t>-2,35; 14,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 26,89</t>
+          <t>-15,65; 12,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,51; —</t>
+          <t>-66,95; inf</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 652,31</t>
+          <t>-78,01; 283,79</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-2,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-31,63%</t>
+          <t>-27,6%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -2,36</t>
+          <t>-12,98; -2,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,22</t>
+          <t>-5,59; 6,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -1,3</t>
+          <t>-15,14; -1,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 5,08</t>
+          <t>-10,82; 6,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,13</t>
+          <t>-100,0; 49,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,39; 148,06</t>
+          <t>-78,61; 160,78</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,81%</t>
+          <t>-5,62%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 14,93</t>
+          <t>-1,35; 15,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 3,81</t>
+          <t>-11,1; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 19,11</t>
+          <t>-0,14; 19,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 8,29</t>
+          <t>-10,63; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 13,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 0,07</t>
+          <t>-17,45; -0,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 17,89</t>
+          <t>-3,35; 17,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 14,91</t>
+          <t>-13,68; 14,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 792,22</t>
+          <t>-42,43; 907,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 519,24</t>
+          <t>-77,95; 382,24</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>-2,67%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 25,79</t>
+          <t>-8,48; 28,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 14,53</t>
+          <t>-7,14; 14,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 21,86</t>
+          <t>-29,33; 23,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 14,44</t>
+          <t>-18,31; 13,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 621,4</t>
+          <t>-43,81; 710,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 35,84</t>
+          <t>-35,72; 38,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 22,34</t>
+          <t>-23,53; 19,84</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 12,11</t>
+          <t>-7,46; 12,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 6,7</t>
+          <t>-12,81; 7,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 21,59</t>
+          <t>-9,29; 24,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,7</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 360,21</t>
+          <t>-100,0; 435,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 195,48</t>
+          <t>-34,47; 201,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,29</t>
+          <t>-4,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-25,17%</t>
+          <t>-21,31%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 7,68</t>
+          <t>-6,3; 8,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 8,05</t>
+          <t>-4,08; 7,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 0,42</t>
+          <t>-22,28; -0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 5,06</t>
+          <t>-17,93; 6,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 235,15</t>
+          <t>-69,02; 275,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-80,77; 816,87</t>
+          <t>-81,87; 656,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 4,37</t>
+          <t>-70,41; -0,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,08; 36,54</t>
+          <t>-62,47; 42,4</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-1,79%</t>
+          <t>-1,16%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 3,66</t>
+          <t>-10,53; 3,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 10,68</t>
+          <t>-6,6; 9,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 13,34</t>
+          <t>-11,34; 12,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 8,75</t>
+          <t>-10,53; 8,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 55,59</t>
+          <t>-70,57; 56,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 237,94</t>
+          <t>-49,4; 190,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 51,9</t>
+          <t>-29,92; 50,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 11,25</t>
+          <t>-12,15; 10,45</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-5,64%</t>
+          <t>-6,99%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,83</t>
+          <t>-2,18; 4,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,19</t>
+          <t>-3,45; 2,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,63</t>
+          <t>-5,33; 4,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,39</t>
+          <t>-8,31; 2,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,54</t>
+          <t>-28,06; 77,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 46,43</t>
+          <t>-43,59; 44,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 26,7</t>
+          <t>-24,63; 24,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 15,02</t>
+          <t>-22,64; 10,19</t>
         </is>
       </c>
     </row>
